--- a/archives_posts/votation_allegement_primes2024_vox/3230_Vox_145_Doc_Codebook_DE-FR-IT.xlsx
+++ b/archives_posts/votation_allegement_primes2024_vox/3230_Vox_145_Doc_Codebook_DE-FR-IT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gueney\Documents\GitHub\celalguney\archives_posts\votation_allegement_primes2024_vox\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\celal\Documents\GitHub\celalguney\archives_posts\votation_allegement_primes2024_vox\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1BB89C-772B-4300-9225-B57C4226AEBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C04C11-D0C5-400D-B37C-D4FD1DAA36A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="315" yWindow="510" windowWidth="28485" windowHeight="14970" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LCA 7 classes" sheetId="5" r:id="rId1"/>
@@ -22,19 +22,6 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Codebook!$A$1:$E$2231</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -7123,12 +7110,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7155,6 +7136,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -8416,36 +8403,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2B3EA10-774F-4FBE-BD7A-ED829CD96A29}">
   <dimension ref="A1:K849"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.59765625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="36.81640625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" style="25" customWidth="1"/>
-    <col min="3" max="3" width="14.81640625" style="25" customWidth="1"/>
-    <col min="4" max="6" width="10.6328125" style="25"/>
-    <col min="7" max="7" width="11.453125" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.6328125" style="25"/>
+    <col min="1" max="1" width="36.796875" style="25" customWidth="1"/>
+    <col min="2" max="2" width="14.46484375" style="25" customWidth="1"/>
+    <col min="3" max="3" width="14.796875" style="25" customWidth="1"/>
+    <col min="4" max="6" width="10.59765625" style="25"/>
+    <col min="7" max="7" width="11.46484375" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="10.59765625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="43.5">
-      <c r="B1" s="86" t="s">
+    <row r="1" spans="1:9" ht="42.75">
+      <c r="B1" s="84" t="s">
         <v>2166</v>
       </c>
-      <c r="C1" s="88" t="s">
+      <c r="C1" s="86" t="s">
         <v>2165</v>
       </c>
-      <c r="D1" s="87" t="s">
+      <c r="D1" s="85" t="s">
         <v>2160</v>
       </c>
-      <c r="E1" s="85" t="s">
+      <c r="E1" s="83" t="s">
         <v>2161</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="87" t="s">
         <v>2162</v>
       </c>
       <c r="G1" s="25" t="s">
         <v>2164</v>
       </c>
-      <c r="H1" s="85" t="s">
+      <c r="H1" s="83" t="s">
         <v>2163</v>
       </c>
     </row>
@@ -8516,7 +8503,7 @@
       <c r="H4" s="73"/>
       <c r="I4" s="73"/>
     </row>
-    <row r="5" spans="1:9" ht="29">
+    <row r="5" spans="1:9" ht="28.5">
       <c r="A5" s="72" t="s">
         <v>1784</v>
       </c>
@@ -8716,7 +8703,7 @@
         <v>0.6613</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="29">
+    <row r="13" spans="1:9" ht="28.5">
       <c r="A13" s="72" t="s">
         <v>1792</v>
       </c>
@@ -9016,7 +9003,7 @@
         <v>0.80449999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="29">
+    <row r="25" spans="1:9" ht="28.5">
       <c r="A25" s="72" t="s">
         <v>1804</v>
       </c>
@@ -9116,7 +9103,7 @@
         <v>0.59540000000000004</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="29">
+    <row r="29" spans="1:9" ht="28.5">
       <c r="A29" s="72" t="s">
         <v>1808</v>
       </c>
@@ -9216,7 +9203,7 @@
         <v>0.65390000000000004</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="29">
+    <row r="33" spans="1:9" ht="28.5">
       <c r="A33" s="72" t="s">
         <v>1812</v>
       </c>
@@ -10277,7 +10264,7 @@
         <v>4.1700000000000001E-2</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="29">
+    <row r="74" spans="1:9" ht="28.5">
       <c r="A74" s="70" t="s">
         <v>2006</v>
       </c>
@@ -10809,7 +10796,7 @@
         <v>5.2499999999999998E-2</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="29">
+    <row r="94" spans="1:9" ht="28.5">
       <c r="A94" s="70" t="s">
         <v>203</v>
       </c>
@@ -11054,7 +11041,7 @@
       <c r="H102" s="73"/>
       <c r="I102" s="73"/>
     </row>
-    <row r="103" spans="1:9" ht="29">
+    <row r="103" spans="1:9" ht="28.5">
       <c r="A103" s="70" t="s">
         <v>209</v>
       </c>
@@ -11257,7 +11244,7 @@
         <v>2.7099999999999999E-2</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="29">
+    <row r="110" spans="1:9" ht="28.5">
       <c r="A110" s="70" t="s">
         <v>2025</v>
       </c>
@@ -11444,7 +11431,7 @@
         <v>7.8299999999999995E-2</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="29">
+    <row r="117" spans="1:9" ht="28.5">
       <c r="A117" s="70" t="s">
         <v>826</v>
       </c>
@@ -11589,7 +11576,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="29">
+    <row r="122" spans="1:9" ht="28.5">
       <c r="A122" s="70" t="s">
         <v>46</v>
       </c>
@@ -11618,7 +11605,7 @@
         <v>0.2324</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="29">
+    <row r="123" spans="1:9" ht="28.5">
       <c r="A123" s="70" t="s">
         <v>645</v>
       </c>
@@ -11776,7 +11763,7 @@
         <v>4.9700000000000001E-2</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="29">
+    <row r="129" spans="1:9" ht="28.5">
       <c r="A129" s="70" t="s">
         <v>2030</v>
       </c>
@@ -12121,7 +12108,7 @@
         <v>0.50970000000000004</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="29">
+    <row r="142" spans="1:9" ht="28.5">
       <c r="A142" s="70" t="s">
         <v>2033</v>
       </c>
@@ -12250,7 +12237,7 @@
       <c r="H146" s="73"/>
       <c r="I146" s="73"/>
     </row>
-    <row r="147" spans="1:9" ht="29">
+    <row r="147" spans="1:9" ht="28.5">
       <c r="A147" s="70" t="s">
         <v>209</v>
       </c>
@@ -12453,7 +12440,7 @@
         <v>1.0800000000000001E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="29">
+    <row r="154" spans="1:9" ht="28.5">
       <c r="A154" s="70" t="s">
         <v>2025</v>
       </c>
@@ -13112,7 +13099,7 @@
         <v>0.1573</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="87">
+    <row r="177" spans="1:9" ht="71.25">
       <c r="A177" s="72" t="s">
         <v>2155</v>
       </c>
@@ -14035,7 +14022,7 @@
         <v>0.1391</v>
       </c>
     </row>
-    <row r="210" spans="1:9" s="78" customFormat="1" ht="29">
+    <row r="210" spans="1:9" s="78" customFormat="1" ht="28.5">
       <c r="A210" s="77" t="s">
         <v>2159</v>
       </c>
@@ -14106,7 +14093,7 @@
         <v>0.3327</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="29">
+    <row r="213" spans="1:9" ht="28.5">
       <c r="A213" s="70" t="s">
         <v>164</v>
       </c>
@@ -15144,7 +15131,7 @@
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="251" spans="1:9" s="78" customFormat="1" ht="29">
+    <row r="251" spans="1:9" s="78" customFormat="1" ht="28.5">
       <c r="A251" s="77" t="s">
         <v>2156</v>
       </c>
@@ -15215,7 +15202,7 @@
         <v>0.36230000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="29">
+    <row r="254" spans="1:9" ht="28.5">
       <c r="A254" s="70" t="s">
         <v>164</v>
       </c>
@@ -15863,7 +15850,7 @@
         <v>0.98219999999999996</v>
       </c>
     </row>
-    <row r="278" spans="1:9" ht="29">
+    <row r="278" spans="1:9" ht="28.5">
       <c r="A278" s="72" t="s">
         <v>2157</v>
       </c>
@@ -15934,7 +15921,7 @@
         <v>0.44409999999999999</v>
       </c>
     </row>
-    <row r="281" spans="1:9" ht="29">
+    <row r="281" spans="1:9" ht="28.5">
       <c r="A281" s="70" t="s">
         <v>164</v>
       </c>
@@ -16943,7 +16930,7 @@
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="318" spans="1:9" ht="29">
+    <row r="318" spans="1:9" ht="28.5">
       <c r="A318" s="72" t="s">
         <v>2158</v>
       </c>
@@ -17014,7 +17001,7 @@
         <v>0.1273</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="29">
+    <row r="321" spans="1:9" ht="28.5">
       <c r="A321" s="70" t="s">
         <v>164</v>
       </c>
@@ -31261,7 +31248,7 @@
         <v>5.3499999999999999E-2</v>
       </c>
     </row>
-    <row r="842" spans="1:9" ht="29">
+    <row r="842" spans="1:9" ht="28.5">
       <c r="A842" s="70" t="s">
         <v>2006</v>
       </c>
@@ -31501,16 +31488,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E2231"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.36328125" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="91.7265625" style="33" customWidth="1"/>
-    <col min="4" max="4" width="94.08984375" style="33" customWidth="1"/>
-    <col min="5" max="5" width="94.08984375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="25.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="91.73046875" style="33" customWidth="1"/>
+    <col min="4" max="4" width="94.06640625" style="33" customWidth="1"/>
+    <col min="5" max="5" width="94.06640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="65" customFormat="1" ht="18.5">
+    <row r="1" spans="1:5" s="65" customFormat="1" ht="18">
       <c r="A1" s="4" t="s">
         <v>661</v>
       </c>
@@ -31585,7 +31572,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43.5">
+    <row r="6" spans="1:5" ht="42.75">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>235</v>
@@ -31645,7 +31632,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29">
+    <row r="10" spans="1:5" ht="28.5">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>238</v>
@@ -31735,7 +31722,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="29">
+    <row r="16" spans="1:5" ht="28.5">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>654</v>
@@ -35650,7 +35637,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="285" spans="2:5" s="25" customFormat="1" ht="43.5">
+    <row r="285" spans="2:5" s="25" customFormat="1" ht="42.75">
       <c r="B285" s="5">
         <v>55</v>
       </c>
@@ -36602,7 +36589,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="351" spans="1:5" s="25" customFormat="1" ht="43.5">
+    <row r="351" spans="1:5" s="25" customFormat="1" ht="42.75">
       <c r="B351" s="5">
         <v>55</v>
       </c>
@@ -37057,7 +37044,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="383" spans="1:5" ht="58">
+    <row r="383" spans="1:5" ht="57">
       <c r="A383" s="25"/>
       <c r="B383" s="25" t="s">
         <v>683</v>
@@ -37162,7 +37149,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="390" spans="1:5" ht="58">
+    <row r="390" spans="1:5" ht="57">
       <c r="A390" s="25"/>
       <c r="B390" s="25" t="s">
         <v>684</v>
@@ -37267,7 +37254,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="397" spans="1:5" ht="58">
+    <row r="397" spans="1:5" ht="57">
       <c r="A397" s="5"/>
       <c r="B397" s="25" t="s">
         <v>685</v>
@@ -37372,7 +37359,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="404" spans="1:5" ht="29">
+    <row r="404" spans="1:5" ht="28.5">
       <c r="A404" s="5"/>
       <c r="B404" s="25" t="s">
         <v>148</v>
@@ -37867,7 +37854,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="437" spans="1:5" ht="29">
+    <row r="437" spans="1:5">
       <c r="A437" s="5"/>
       <c r="B437" s="5">
         <v>35</v>
@@ -37942,7 +37929,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="442" spans="1:5" ht="29">
+    <row r="442" spans="1:5" ht="28.5">
       <c r="A442" s="5"/>
       <c r="B442" s="5">
         <v>42</v>
@@ -38570,7 +38557,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="484" spans="1:5" ht="29">
+    <row r="484" spans="1:5">
       <c r="A484" s="5"/>
       <c r="B484" s="5">
         <v>35</v>
@@ -38645,7 +38632,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="489" spans="1:5" ht="29">
+    <row r="489" spans="1:5" ht="28.5">
       <c r="A489" s="5"/>
       <c r="B489" s="5">
         <v>42</v>
@@ -39423,7 +39410,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="543" spans="2:5" ht="29">
+    <row r="543" spans="2:5" ht="28.5">
       <c r="B543">
         <v>45</v>
       </c>
@@ -39465,7 +39452,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="546" spans="1:5" ht="29">
+    <row r="546" spans="1:5" ht="28.5">
       <c r="B546">
         <v>51</v>
       </c>
@@ -40139,7 +40126,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="594" spans="2:5" ht="29">
+    <row r="594" spans="2:5" ht="28.5">
       <c r="B594">
         <v>45</v>
       </c>
@@ -40181,7 +40168,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="597" spans="2:5" ht="29">
+    <row r="597" spans="2:5" ht="28.5">
       <c r="B597">
         <v>51</v>
       </c>
@@ -40510,7 +40497,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="620" spans="1:5" ht="58">
+    <row r="620" spans="1:5" ht="57">
       <c r="A620" s="5"/>
       <c r="B620" s="25" t="s">
         <v>776</v>
@@ -40615,7 +40602,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="627" spans="1:5" ht="58">
+    <row r="627" spans="1:5" ht="57">
       <c r="A627" s="5"/>
       <c r="B627" s="25" t="s">
         <v>777</v>
@@ -40720,7 +40707,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="634" spans="1:5" ht="58">
+    <row r="634" spans="1:5" ht="57">
       <c r="A634" s="5"/>
       <c r="B634" s="25" t="s">
         <v>778</v>
@@ -40825,7 +40812,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="641" spans="1:5" ht="29">
+    <row r="641" spans="1:5" ht="28.5">
       <c r="A641" s="5"/>
       <c r="B641" s="25" t="s">
         <v>779</v>
@@ -41274,7 +41261,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="672" spans="2:5" ht="29">
+    <row r="672" spans="2:5">
       <c r="B672">
         <v>34</v>
       </c>
@@ -41330,7 +41317,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="676" spans="2:5" ht="29">
+    <row r="676" spans="2:5" ht="28.5">
       <c r="B676">
         <v>52</v>
       </c>
@@ -41414,7 +41401,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="682" spans="2:5" ht="29">
+    <row r="682" spans="2:5" ht="28.5">
       <c r="B682">
         <v>62</v>
       </c>
@@ -41428,7 +41415,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="683" spans="2:5" ht="29">
+    <row r="683" spans="2:5" ht="28.5">
       <c r="B683">
         <v>63</v>
       </c>
@@ -41878,7 +41865,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="715" spans="2:5" ht="29">
+    <row r="715" spans="2:5">
       <c r="B715">
         <v>34</v>
       </c>
@@ -41934,7 +41921,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="719" spans="2:5" ht="29">
+    <row r="719" spans="2:5" ht="28.5">
       <c r="B719">
         <v>52</v>
       </c>
@@ -42018,7 +42005,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="725" spans="2:5" ht="29">
+    <row r="725" spans="2:5" ht="28.5">
       <c r="B725">
         <v>62</v>
       </c>
@@ -42032,7 +42019,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="726" spans="2:5" ht="29">
+    <row r="726" spans="2:5" ht="28.5">
       <c r="B726">
         <v>63</v>
       </c>
@@ -42524,7 +42511,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="761" spans="2:5" ht="29">
+    <row r="761" spans="2:5" ht="28.5">
       <c r="B761">
         <v>35</v>
       </c>
@@ -42594,7 +42581,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="766" spans="2:5" ht="29">
+    <row r="766" spans="2:5" ht="28.5">
       <c r="B766">
         <v>43</v>
       </c>
@@ -43100,7 +43087,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="802" spans="2:5" ht="29">
+    <row r="802" spans="2:5" ht="28.5">
       <c r="B802">
         <v>35</v>
       </c>
@@ -43170,7 +43157,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="807" spans="2:5" ht="29">
+    <row r="807" spans="2:5" ht="28.5">
       <c r="B807">
         <v>43</v>
       </c>
@@ -43485,7 +43472,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="829" spans="1:5" ht="58">
+    <row r="829" spans="1:5" ht="57">
       <c r="A829" s="5"/>
       <c r="B829" s="25" t="s">
         <v>895</v>
@@ -43590,7 +43577,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="836" spans="1:5" ht="58">
+    <row r="836" spans="1:5" ht="57">
       <c r="A836" s="5"/>
       <c r="B836" s="25" t="s">
         <v>896</v>
@@ -43695,7 +43682,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="843" spans="1:5" ht="58">
+    <row r="843" spans="1:5" ht="57">
       <c r="A843" s="5"/>
       <c r="B843" s="25" t="s">
         <v>897</v>
@@ -45527,7 +45514,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="972" spans="1:5" ht="29">
+    <row r="972" spans="1:5" ht="28.5">
       <c r="B972">
         <v>21</v>
       </c>
@@ -45541,7 +45528,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="973" spans="1:5" ht="29">
+    <row r="973" spans="1:5">
       <c r="B973">
         <v>22</v>
       </c>
@@ -45569,7 +45556,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="975" spans="1:5" ht="29">
+    <row r="975" spans="1:5" ht="28.5">
       <c r="B975">
         <v>24</v>
       </c>
@@ -45583,7 +45570,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="976" spans="1:5" ht="29">
+    <row r="976" spans="1:5" ht="28.5">
       <c r="B976">
         <v>25</v>
       </c>
@@ -45597,7 +45584,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="977" spans="2:5" ht="29">
+    <row r="977" spans="2:5">
       <c r="B977">
         <v>26</v>
       </c>
@@ -46229,7 +46216,7 @@
         <v>1641</v>
       </c>
     </row>
-    <row r="1022" spans="1:5" ht="29">
+    <row r="1022" spans="1:5" ht="28.5">
       <c r="B1022">
         <v>21</v>
       </c>
@@ -46243,7 +46230,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="1023" spans="1:5" ht="29">
+    <row r="1023" spans="1:5">
       <c r="B1023">
         <v>22</v>
       </c>
@@ -46271,7 +46258,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="1025" spans="2:5" ht="29">
+    <row r="1025" spans="2:5" ht="28.5">
       <c r="B1025">
         <v>24</v>
       </c>
@@ -46285,7 +46272,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="1026" spans="2:5" ht="29">
+    <row r="1026" spans="2:5" ht="28.5">
       <c r="B1026">
         <v>25</v>
       </c>
@@ -46299,7 +46286,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="1027" spans="2:5" ht="29">
+    <row r="1027" spans="2:5">
       <c r="B1027">
         <v>26</v>
       </c>
@@ -46790,7 +46777,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="1062" spans="1:5" ht="29">
+    <row r="1062" spans="1:5" ht="28.5">
       <c r="A1062" s="5"/>
       <c r="B1062" s="5"/>
       <c r="C1062" s="6" t="s">
@@ -50795,7 +50782,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1329" spans="1:5" ht="43.5">
+    <row r="1329" spans="1:5" ht="42.75">
       <c r="A1329" s="5"/>
       <c r="B1329" t="s">
         <v>17</v>
@@ -50990,7 +50977,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1342" spans="1:5" ht="29">
+    <row r="1342" spans="1:5" ht="28.5">
       <c r="A1342" s="5"/>
       <c r="B1342" s="5" t="s">
         <v>905</v>
@@ -51125,7 +51112,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1351" spans="1:5" ht="29">
+    <row r="1351" spans="1:5" ht="28.5">
       <c r="A1351" s="5"/>
       <c r="B1351" s="5" t="s">
         <v>859</v>
@@ -51260,7 +51247,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1360" spans="1:5" ht="29">
+    <row r="1360" spans="1:5" ht="28.5">
       <c r="A1360" s="5"/>
       <c r="B1360" s="5" t="s">
         <v>815</v>
@@ -51395,7 +51382,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1369" spans="1:5" ht="29">
+    <row r="1369" spans="1:5" ht="28.5">
       <c r="A1369" s="5"/>
       <c r="B1369" s="48" t="s">
         <v>1721</v>
@@ -51530,7 +51517,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1378" spans="1:5" ht="29">
+    <row r="1378" spans="1:5" ht="28.5">
       <c r="A1378" s="5"/>
       <c r="B1378" s="5" t="s">
         <v>921</v>
@@ -51800,7 +51787,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="1396" spans="1:5" ht="29">
+    <row r="1396" spans="1:5" ht="28.5">
       <c r="A1396" s="5"/>
       <c r="B1396" s="5" t="s">
         <v>18</v>
@@ -51965,7 +51952,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1407" spans="1:5" s="11" customFormat="1" ht="29">
+    <row r="1407" spans="1:5" s="11" customFormat="1" ht="28.5">
       <c r="A1407" s="5"/>
       <c r="B1407" s="5"/>
       <c r="C1407" s="14" t="s">
@@ -51978,7 +51965,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="1408" spans="1:5" ht="29">
+    <row r="1408" spans="1:5" ht="28.5">
       <c r="A1408" s="5"/>
       <c r="B1408" s="5" t="s">
         <v>692</v>
@@ -52083,7 +52070,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1415" spans="1:5" ht="29">
+    <row r="1415" spans="1:5" ht="28.5">
       <c r="A1415" s="5"/>
       <c r="B1415" s="5" t="s">
         <v>693</v>
@@ -52188,7 +52175,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1422" spans="1:5" ht="43.5">
+    <row r="1422" spans="1:5" ht="28.5">
       <c r="A1422" s="5"/>
       <c r="B1422" s="5" t="s">
         <v>694</v>
@@ -52295,7 +52282,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1429" spans="1:5" ht="29">
+    <row r="1429" spans="1:5" ht="28.5">
       <c r="A1429" s="5"/>
       <c r="B1429" s="5" t="s">
         <v>695</v>
@@ -52505,7 +52492,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1443" spans="1:5" ht="29">
+    <row r="1443" spans="1:5" ht="28.5">
       <c r="A1443" s="5"/>
       <c r="B1443" s="5" t="s">
         <v>697</v>
@@ -52610,7 +52597,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1450" spans="1:5" ht="29">
+    <row r="1450" spans="1:5" ht="28.5">
       <c r="A1450" s="5"/>
       <c r="B1450" s="5" t="s">
         <v>134</v>
@@ -52775,7 +52762,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1461" spans="1:5" ht="29">
+    <row r="1461" spans="1:5" ht="28.5">
       <c r="A1461" s="5"/>
       <c r="B1461" s="5"/>
       <c r="C1461" s="21" t="s">
@@ -52788,7 +52775,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="1462" spans="1:5" ht="29">
+    <row r="1462" spans="1:5" ht="28.5">
       <c r="A1462" s="5"/>
       <c r="B1462" s="12" t="s">
         <v>698</v>
@@ -52893,7 +52880,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1469" spans="1:5" ht="29">
+    <row r="1469" spans="1:5" ht="28.5">
       <c r="A1469" s="5"/>
       <c r="B1469" s="12" t="s">
         <v>699</v>
@@ -52998,7 +52985,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1476" spans="1:5" ht="29">
+    <row r="1476" spans="1:5" ht="28.5">
       <c r="A1476" s="5"/>
       <c r="B1476" s="12" t="s">
         <v>700</v>
@@ -53105,7 +53092,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1483" spans="1:5" ht="29">
+    <row r="1483" spans="1:5" ht="28.5">
       <c r="A1483" s="5"/>
       <c r="B1483" s="12" t="s">
         <v>701</v>
@@ -53210,7 +53197,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1490" spans="1:5" ht="29">
+    <row r="1490" spans="1:5" ht="28.5">
       <c r="A1490" s="5"/>
       <c r="B1490" s="12" t="s">
         <v>702</v>
@@ -53315,7 +53302,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1497" spans="1:5" ht="29">
+    <row r="1497" spans="1:5" ht="28.5">
       <c r="A1497" s="5"/>
       <c r="B1497" s="12" t="s">
         <v>703</v>
@@ -53420,7 +53407,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1504" spans="1:5" ht="43.5">
+    <row r="1504" spans="1:5" ht="42.75">
       <c r="B1504" s="48"/>
       <c r="C1504" s="21" t="s">
         <v>1779</v>
@@ -54104,7 +54091,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1553" spans="1:5" ht="29">
+    <row r="1553" spans="1:5" ht="28.5">
       <c r="A1553" s="5"/>
       <c r="B1553" s="5" t="s">
         <v>784</v>
@@ -54269,7 +54256,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1564" spans="1:5" ht="29">
+    <row r="1564" spans="1:5" ht="28.5">
       <c r="A1564" s="5"/>
       <c r="B1564" s="5"/>
       <c r="C1564" s="21" t="s">
@@ -54282,7 +54269,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="1565" spans="1:5" ht="29">
+    <row r="1565" spans="1:5" ht="28.5">
       <c r="A1565" s="12"/>
       <c r="B1565" s="12" t="s">
         <v>787</v>
@@ -54387,7 +54374,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1572" spans="1:5" ht="29">
+    <row r="1572" spans="1:5" ht="28.5">
       <c r="A1572" s="5"/>
       <c r="B1572" s="12" t="s">
         <v>788</v>
@@ -54492,7 +54479,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1579" spans="1:5" ht="29">
+    <row r="1579" spans="1:5" ht="28.5">
       <c r="A1579" s="5"/>
       <c r="B1579" s="12" t="s">
         <v>789</v>
@@ -54599,7 +54586,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1586" spans="1:5" ht="29">
+    <row r="1586" spans="1:5" ht="28.5">
       <c r="A1586" s="5"/>
       <c r="B1586" s="12" t="s">
         <v>790</v>
@@ -54704,7 +54691,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1593" spans="1:5" ht="29">
+    <row r="1593" spans="1:5" ht="28.5">
       <c r="A1593" s="5"/>
       <c r="B1593" s="12" t="s">
         <v>791</v>
@@ -54809,7 +54796,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1600" spans="1:5" ht="29">
+    <row r="1600" spans="1:5" ht="28.5">
       <c r="A1600" s="5"/>
       <c r="B1600" s="12" t="s">
         <v>792</v>
@@ -54914,7 +54901,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1607" spans="1:5" ht="43.5">
+    <row r="1607" spans="1:5" ht="42.75">
       <c r="B1607" s="48"/>
       <c r="C1607" s="21" t="s">
         <v>1841</v>
@@ -54926,7 +54913,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="1608" spans="1:5" ht="29">
+    <row r="1608" spans="1:5" ht="28.5">
       <c r="B1608" s="48" t="s">
         <v>1844</v>
       </c>
@@ -55010,7 +54997,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1614" spans="1:5" ht="29">
+    <row r="1614" spans="1:5" ht="28.5">
       <c r="B1614" s="48" t="s">
         <v>1848</v>
       </c>
@@ -55094,7 +55081,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1620" spans="1:5" ht="29">
+    <row r="1620" spans="1:5" ht="28.5">
       <c r="A1620" s="5"/>
       <c r="B1620" s="5" t="s">
         <v>941</v>
@@ -55259,7 +55246,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1631" spans="1:5" ht="29">
+    <row r="1631" spans="1:5" ht="28.5">
       <c r="A1631" s="5"/>
       <c r="B1631" s="5"/>
       <c r="C1631" s="21" t="s">
@@ -55272,7 +55259,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="1632" spans="1:5" ht="29">
+    <row r="1632" spans="1:5" ht="28.5">
       <c r="A1632" s="12"/>
       <c r="B1632" s="12" t="s">
         <v>943</v>
@@ -55377,7 +55364,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1639" spans="1:5" ht="29">
+    <row r="1639" spans="1:5" ht="28.5">
       <c r="A1639" s="5"/>
       <c r="B1639" s="12" t="s">
         <v>944</v>
@@ -55482,7 +55469,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1646" spans="1:5" ht="29">
+    <row r="1646" spans="1:5" ht="28.5">
       <c r="A1646" s="5"/>
       <c r="B1646" s="12" t="s">
         <v>945</v>
@@ -55589,7 +55576,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1653" spans="1:5" ht="29">
+    <row r="1653" spans="1:5" ht="28.5">
       <c r="A1653" s="5"/>
       <c r="B1653" s="12" t="s">
         <v>946</v>
@@ -55694,7 +55681,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1660" spans="1:5" ht="29">
+    <row r="1660" spans="1:5" ht="28.5">
       <c r="A1660" s="5"/>
       <c r="B1660" s="12" t="s">
         <v>947</v>
@@ -55799,7 +55786,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1667" spans="1:5" ht="29">
+    <row r="1667" spans="1:5" ht="28.5">
       <c r="A1667" s="5"/>
       <c r="B1667" s="12" t="s">
         <v>948</v>
@@ -55904,7 +55891,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1674" spans="1:5" ht="29">
+    <row r="1674" spans="1:5" ht="28.5">
       <c r="B1674" s="48"/>
       <c r="C1674" s="21" t="s">
         <v>1879</v>
@@ -56084,7 +56071,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1687" spans="2:5" ht="29">
+    <row r="1687" spans="2:5" ht="28.5">
       <c r="B1687" s="11" t="s">
         <v>1890</v>
       </c>
@@ -56168,7 +56155,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1693" spans="2:5" ht="29">
+    <row r="1693" spans="2:5" ht="28.5">
       <c r="B1693" s="11" t="s">
         <v>1894</v>
       </c>
@@ -56252,7 +56239,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="1699" spans="1:5" ht="29">
+    <row r="1699" spans="1:5" ht="28.5">
       <c r="B1699" s="11" t="s">
         <v>1898</v>
       </c>
@@ -56441,7 +56428,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1712" spans="1:5" ht="43.5">
+    <row r="1712" spans="1:5" ht="42.75">
       <c r="A1712" s="5"/>
       <c r="B1712" s="5"/>
       <c r="C1712" s="6" t="s">
@@ -59606,7 +59593,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="1923" spans="1:5" ht="29">
+    <row r="1923" spans="1:5" ht="28.5">
       <c r="A1923" s="5"/>
       <c r="B1923" s="5"/>
       <c r="C1923" s="6" t="s">
@@ -61301,7 +61288,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2036" spans="1:5" ht="29">
+    <row r="2036" spans="1:5" ht="28.5">
       <c r="A2036" s="5"/>
       <c r="B2036" s="5" t="s">
         <v>23</v>
@@ -61511,7 +61498,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2050" spans="1:5" ht="29">
+    <row r="2050" spans="1:5" ht="28.5">
       <c r="A2050" s="5"/>
       <c r="B2050" s="5" t="s">
         <v>26</v>
@@ -61706,7 +61693,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="2063" spans="1:5" ht="72.5">
+    <row r="2063" spans="1:5" ht="71.25">
       <c r="A2063" s="5"/>
       <c r="B2063" s="5" t="s">
         <v>12</v>
@@ -62486,7 +62473,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="2115" spans="1:5" ht="29">
+    <row r="2115" spans="1:5" ht="28.5">
       <c r="A2115" s="5"/>
       <c r="B2115" s="5">
         <v>31</v>
@@ -62501,7 +62488,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2116" spans="1:5" ht="43.5">
+    <row r="2116" spans="1:5" ht="28.5">
       <c r="A2116" s="5"/>
       <c r="B2116" s="5">
         <v>32</v>
@@ -62546,7 +62533,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="2119" spans="1:5" ht="29">
+    <row r="2119" spans="1:5" ht="28.5">
       <c r="A2119" s="5"/>
       <c r="B2119" s="5">
         <v>51</v>
@@ -62561,7 +62548,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="2120" spans="1:5" ht="29">
+    <row r="2120" spans="1:5" ht="28.5">
       <c r="A2120" s="5"/>
       <c r="B2120" s="5">
         <v>52</v>
@@ -63431,7 +63418,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="2178" spans="1:5" ht="29">
+    <row r="2178" spans="1:5" ht="28.5">
       <c r="A2178" s="5"/>
       <c r="B2178" s="5">
         <v>31</v>
@@ -63446,7 +63433,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="2179" spans="1:5" ht="43.5">
+    <row r="2179" spans="1:5" ht="28.5">
       <c r="A2179" s="5"/>
       <c r="B2179" s="5">
         <v>32</v>
@@ -63491,7 +63478,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="2182" spans="1:5" ht="29">
+    <row r="2182" spans="1:5" ht="28.5">
       <c r="A2182" s="5"/>
       <c r="B2182" s="5">
         <v>51</v>
@@ -63506,7 +63493,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="2183" spans="1:5" ht="29">
+    <row r="2183" spans="1:5" ht="28.5">
       <c r="A2183" s="5"/>
       <c r="B2183" s="5">
         <v>52</v>
@@ -63581,7 +63568,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2188" spans="1:5" ht="29">
+    <row r="2188" spans="1:5" ht="28.5">
       <c r="A2188" s="5"/>
       <c r="B2188" s="5" t="s">
         <v>142</v>
@@ -63761,7 +63748,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="2200" spans="1:5" ht="58">
+    <row r="2200" spans="1:5" ht="57">
       <c r="A2200" s="5"/>
       <c r="B2200" s="5" t="s">
         <v>53</v>
@@ -64016,7 +64003,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="2217" spans="1:5" ht="29">
+    <row r="2217" spans="1:5" ht="28.5">
       <c r="A2217" s="5"/>
       <c r="B2217" s="5" t="s">
         <v>143</v>
@@ -64251,7 +64238,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C97DEC3-E03C-4C2D-A881-D575004AB0FC}">
   <dimension ref="B1:C51"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="2:3">
       <c r="B1">
@@ -64261,7 +64248,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="2" spans="2:3" ht="58">
+    <row r="2" spans="2:3" ht="57">
       <c r="B2">
         <v>11</v>
       </c>
@@ -64269,7 +64256,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="87">
+    <row r="3" spans="2:3" ht="85.5">
       <c r="B3">
         <v>12</v>
       </c>
@@ -64277,7 +64264,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="4" spans="2:3" ht="116">
+    <row r="4" spans="2:3" ht="114">
       <c r="B4">
         <v>13</v>
       </c>
@@ -64285,7 +64272,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="29">
+    <row r="5" spans="2:3">
       <c r="B5">
         <v>14</v>
       </c>
@@ -64293,7 +64280,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="29">
+    <row r="6" spans="2:3" ht="28.5">
       <c r="B6">
         <v>15</v>
       </c>
@@ -64301,7 +64288,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="29">
+    <row r="7" spans="2:3" ht="28.5">
       <c r="B7">
         <v>16</v>
       </c>
@@ -64309,7 +64296,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="29">
+    <row r="8" spans="2:3" ht="28.5">
       <c r="B8">
         <v>19</v>
       </c>
@@ -64317,7 +64304,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="10" spans="2:3" ht="58">
+    <row r="10" spans="2:3" ht="57">
       <c r="B10">
         <v>20</v>
       </c>
@@ -64325,7 +64312,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="174">
+    <row r="11" spans="2:3" ht="156.75">
       <c r="B11">
         <v>21</v>
       </c>
@@ -64333,7 +64320,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="145">
+    <row r="12" spans="2:3" ht="142.5">
       <c r="B12">
         <v>22</v>
       </c>
@@ -64341,7 +64328,7 @@
         <v>1597</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="58">
+    <row r="13" spans="2:3" ht="42.75">
       <c r="B13">
         <v>23</v>
       </c>
@@ -64349,7 +64336,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="203">
+    <row r="14" spans="2:3" ht="199.5">
       <c r="B14">
         <v>24</v>
       </c>
@@ -64357,7 +64344,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="174">
+    <row r="15" spans="2:3" ht="142.5">
       <c r="B15">
         <v>25</v>
       </c>
@@ -64365,7 +64352,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="145">
+    <row r="16" spans="2:3" ht="142.5">
       <c r="B16">
         <v>26</v>
       </c>
@@ -64373,7 +64360,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="87">
+    <row r="17" spans="2:3" ht="85.5">
       <c r="B17">
         <v>27</v>
       </c>
@@ -64381,7 +64368,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="72.5">
+    <row r="18" spans="2:3" ht="71.25">
       <c r="B18">
         <v>29</v>
       </c>
@@ -64389,7 +64376,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="43.5">
+    <row r="20" spans="2:3" ht="42.75">
       <c r="B20">
         <v>30</v>
       </c>
@@ -64397,7 +64384,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="58">
+    <row r="21" spans="2:3" ht="57">
       <c r="B21">
         <v>31</v>
       </c>
@@ -64405,7 +64392,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="130.5">
+    <row r="22" spans="2:3" ht="128.25">
       <c r="B22">
         <v>32</v>
       </c>
@@ -64413,7 +64400,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="130.5">
+    <row r="23" spans="2:3" ht="128.25">
       <c r="B23">
         <v>32</v>
       </c>
@@ -64421,7 +64408,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="87">
+    <row r="24" spans="2:3" ht="71.25">
       <c r="B24">
         <v>33</v>
       </c>
@@ -64429,7 +64416,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="25" spans="2:3" ht="72.5">
+    <row r="25" spans="2:3" ht="71.25">
       <c r="B25">
         <v>34</v>
       </c>
@@ -64437,7 +64424,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="26" spans="2:3" ht="72.5">
+    <row r="26" spans="2:3" ht="71.25">
       <c r="B26">
         <v>35</v>
       </c>
@@ -64445,7 +64432,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="27" spans="2:3" ht="116">
+    <row r="27" spans="2:3" ht="114">
       <c r="B27">
         <v>36</v>
       </c>
@@ -64453,7 +64440,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="28" spans="2:3" ht="58">
+    <row r="28" spans="2:3" ht="57">
       <c r="B28">
         <v>39</v>
       </c>
@@ -64461,7 +64448,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="30" spans="2:3" ht="43.5">
+    <row r="30" spans="2:3" ht="28.5">
       <c r="B30">
         <v>40</v>
       </c>
@@ -64469,7 +64456,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="31" spans="2:3" ht="58">
+    <row r="31" spans="2:3" ht="42.75">
       <c r="B31">
         <v>41</v>
       </c>
@@ -64477,7 +64464,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="32" spans="2:3" ht="159.5">
+    <row r="32" spans="2:3" ht="142.5">
       <c r="B32">
         <v>42</v>
       </c>
@@ -64485,7 +64472,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="33" spans="2:3" ht="87">
+    <row r="33" spans="2:3" ht="85.5">
       <c r="B33">
         <v>43</v>
       </c>
@@ -64493,7 +64480,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="34" spans="2:3" ht="87">
+    <row r="34" spans="2:3" ht="85.5">
       <c r="B34">
         <v>44</v>
       </c>
@@ -64501,7 +64488,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="35" spans="2:3" ht="101.5">
+    <row r="35" spans="2:3" ht="99.75">
       <c r="B35">
         <v>45</v>
       </c>
@@ -64509,7 +64496,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="36" spans="2:3" ht="116">
+    <row r="36" spans="2:3" ht="114">
       <c r="B36">
         <v>46</v>
       </c>
@@ -64517,7 +64504,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="37" spans="2:3" ht="72.5">
+    <row r="37" spans="2:3" ht="71.25">
       <c r="B37">
         <v>47</v>
       </c>
@@ -64525,7 +64512,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="38" spans="2:3" ht="43.5">
+    <row r="38" spans="2:3" ht="28.5">
       <c r="B38">
         <v>48</v>
       </c>
@@ -64533,7 +64520,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="39" spans="2:3" ht="58">
+    <row r="39" spans="2:3" ht="42.75">
       <c r="B39">
         <v>49</v>
       </c>
@@ -64549,7 +64536,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="43" spans="2:3" ht="43.5">
+    <row r="43" spans="2:3" ht="42.75">
       <c r="B43">
         <v>91</v>
       </c>
@@ -64557,7 +64544,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="44" spans="2:3" ht="43.5">
+    <row r="44" spans="2:3" ht="42.75">
       <c r="B44">
         <v>92</v>
       </c>
@@ -64565,7 +64552,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="45" spans="2:3" ht="43.5">
+    <row r="45" spans="2:3" ht="42.75">
       <c r="B45">
         <v>93</v>
       </c>
@@ -64573,7 +64560,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="46" spans="2:3" ht="87">
+    <row r="46" spans="2:3" ht="85.5">
       <c r="B46">
         <v>94</v>
       </c>
@@ -64581,7 +64568,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="47" spans="2:3" ht="101.5">
+    <row r="47" spans="2:3" ht="99.75">
       <c r="B47">
         <v>95</v>
       </c>
@@ -64589,7 +64576,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="48" spans="2:3" ht="87">
+    <row r="48" spans="2:3" ht="85.5">
       <c r="B48">
         <v>96</v>
       </c>
@@ -64597,7 +64584,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="49" spans="2:3" ht="58">
+    <row r="49" spans="2:3" ht="57">
       <c r="B49">
         <v>97</v>
       </c>
@@ -64605,7 +64592,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="50" spans="2:3" ht="29">
+    <row r="50" spans="2:3" ht="28.5">
       <c r="B50">
         <v>98</v>
       </c>
@@ -64613,7 +64600,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="51" spans="2:3" ht="29">
+    <row r="51" spans="2:3" ht="28.5">
       <c r="B51">
         <v>99</v>
       </c>
@@ -64629,79 +64616,79 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC8CC5BC-7E89-4F56-8A15-CB519E182F49}">
   <dimension ref="A1:R23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:18" ht="14.25" customHeight="1">
       <c r="A1" s="70" t="s">
         <v>1916</v>
       </c>
-      <c r="B1" s="83" t="s">
+      <c r="B1" s="92" t="s">
         <v>1917</v>
       </c>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="92"/>
+      <c r="R1" s="92"/>
     </row>
     <row r="2" spans="1:18" ht="14.25" customHeight="1">
       <c r="A2" s="70" t="s">
         <v>1918</v>
       </c>
-      <c r="B2" s="84" t="s">
+      <c r="B2" s="93" t="s">
         <v>1919</v>
       </c>
-      <c r="C2" s="84"/>
-      <c r="D2" s="84"/>
-      <c r="E2" s="84"/>
-      <c r="F2" s="84"/>
-      <c r="G2" s="84"/>
-      <c r="H2" s="84"/>
-      <c r="I2" s="84"/>
-      <c r="J2" s="84"/>
-      <c r="K2" s="84"/>
-      <c r="L2" s="84"/>
-      <c r="M2" s="84"/>
-      <c r="N2" s="84"/>
-      <c r="O2" s="84"/>
-      <c r="P2" s="84"/>
-      <c r="Q2" s="84"/>
-      <c r="R2" s="84"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
+      <c r="H2" s="93"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="93"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="93"/>
+      <c r="N2" s="93"/>
+      <c r="O2" s="93"/>
+      <c r="P2" s="93"/>
+      <c r="Q2" s="93"/>
+      <c r="R2" s="93"/>
     </row>
     <row r="3" spans="1:18" ht="14.25" customHeight="1">
       <c r="A3" s="70" t="s">
         <v>1920</v>
       </c>
-      <c r="B3" s="84" t="s">
+      <c r="B3" s="93" t="s">
         <v>1921</v>
       </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-      <c r="J3" s="84"/>
-      <c r="K3" s="84"/>
-      <c r="L3" s="84"/>
-      <c r="M3" s="84"/>
-      <c r="N3" s="84"/>
-      <c r="O3" s="84"/>
-      <c r="P3" s="84"/>
-      <c r="Q3" s="84"/>
-      <c r="R3" s="84"/>
+      <c r="C3" s="93"/>
+      <c r="D3" s="93"/>
+      <c r="E3" s="93"/>
+      <c r="F3" s="93"/>
+      <c r="G3" s="93"/>
+      <c r="H3" s="93"/>
+      <c r="I3" s="93"/>
+      <c r="J3" s="93"/>
+      <c r="K3" s="93"/>
+      <c r="L3" s="93"/>
+      <c r="M3" s="93"/>
+      <c r="N3" s="93"/>
+      <c r="O3" s="93"/>
+      <c r="P3" s="93"/>
+      <c r="Q3" s="93"/>
+      <c r="R3" s="93"/>
     </row>
     <row r="4" spans="1:18">
       <c r="A4" s="72"/>
@@ -65083,59 +65070,59 @@
         <v>0.74580000000000002</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="69" customFormat="1" ht="29">
+    <row r="11" spans="1:18" s="69" customFormat="1" ht="28.5">
       <c r="A11" s="77" t="s">
         <v>1949</v>
       </c>
-      <c r="B11" s="90" t="s">
+      <c r="B11" s="88" t="s">
         <v>1950</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="89">
         <v>-17580.958900000001</v>
       </c>
-      <c r="D11" s="93">
+      <c r="D11" s="91">
         <v>36112.088799999998</v>
       </c>
-      <c r="E11" s="91">
+      <c r="E11" s="89">
         <v>35397.917800000003</v>
       </c>
-      <c r="F11" s="91">
+      <c r="F11" s="89">
         <v>35515.917800000003</v>
       </c>
-      <c r="G11" s="91">
+      <c r="G11" s="89">
         <v>118</v>
       </c>
-      <c r="H11" s="91">
+      <c r="H11" s="89">
         <v>2314.1635999999999</v>
       </c>
-      <c r="I11" s="91">
+      <c r="I11" s="89">
         <v>3023</v>
       </c>
-      <c r="J11" s="92">
+      <c r="J11" s="90">
         <v>1</v>
       </c>
-      <c r="K11" s="92">
+      <c r="K11" s="90">
         <v>0</v>
       </c>
-      <c r="L11" s="92">
+      <c r="L11" s="90">
         <v>24.582799999999999</v>
       </c>
-      <c r="M11" s="92">
+      <c r="M11" s="90">
         <v>154.4409</v>
       </c>
-      <c r="N11" s="92">
+      <c r="N11" s="90">
         <v>0</v>
       </c>
-      <c r="O11" s="92">
+      <c r="O11" s="90">
         <v>154.4409</v>
       </c>
-      <c r="P11" s="92">
+      <c r="P11" s="90">
         <v>0</v>
       </c>
-      <c r="Q11" s="92">
+      <c r="Q11" s="90">
         <v>0.1598</v>
       </c>
-      <c r="R11" s="92">
+      <c r="R11" s="90">
         <v>0.73060000000000003</v>
       </c>
     </row>
